--- a/archivos_vqd/Listado de VQDs Servicios Apocada.xlsx
+++ b/archivos_vqd/Listado de VQDs Servicios Apocada.xlsx
@@ -14,10 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>VQD</t>
   </si>
@@ -71,12 +68,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -387,10 +381,10 @@
   <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="31.290714285714284" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="8.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="37.86214285714286" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="2" width="31.290714285714284" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="2" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="2" width="8.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="2" width="37.86214285714286" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -400,13 +394,11 @@
       <c r="D1" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
@@ -414,7 +406,7 @@
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -422,7 +414,7 @@
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
@@ -430,7 +422,7 @@
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
@@ -438,7 +430,7 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
@@ -446,7 +438,7 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
